--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 DEER BUCK L.E PRIVATE LANDS ONLY.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 DEER BUCK L.E PRIVATE LANDS ONLY.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hunt Table'!$A$1:$O$9</definedName>
@@ -642,7 +642,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
           <t>5.0</t>
@@ -699,7 +703,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
           <t>5.0</t>
@@ -756,7 +764,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
           <t>6.0</t>
